--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3079C76-BA7F-4DD1-94E0-0321D78C165F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A400F2BA-D3B0-4739-84B6-308AF17DCAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="6045" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" customWidth="1"/>
@@ -466,21 +466,21 @@
       </c>
       <c r="E2" s="1">
         <f xml:space="preserve"> D2 + (H2 / F2) * 7</f>
-        <v>46069</v>
+        <v>48381.333333333336</v>
       </c>
       <c r="F2">
         <v>3000</v>
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>9000</v>
+        <v>1000000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>0</v>
+        <v>-985000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -498,21 +498,21 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> D3 + (H3 / F3) * 7</f>
-        <v>46048</v>
+        <v>46069</v>
       </c>
       <c r="F3">
         <v>3000</v>
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>12000</v>
+        <v>21000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>9000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -527,17 +527,25 @@
       </c>
       <c r="E4" s="1">
         <f xml:space="preserve"> D4 + (H4 / F4) * 7</f>
-        <v>46034</v>
+        <v>46048</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H4">
-        <v>12000</v>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>3000</v>
+      </c>
+      <c r="H5">
+        <v>6000</v>
       </c>
     </row>
   </sheetData>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A400F2BA-D3B0-4739-84B6-308AF17DCAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B193A1D2-61BE-47C2-9755-78CE94C983D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>ФИО</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Minako Monster</t>
+  </si>
+  <si>
+    <t>Музохушаев Рахматулло Давлатбекович</t>
   </si>
 </sst>
 </file>
@@ -408,10 +411,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="40.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="20.42578125" customWidth="1"/>
@@ -539,13 +542,44 @@
       <c r="H4">
         <v>16000</v>
       </c>
+      <c r="I4">
+        <f ca="1">((F4)*(G4))-(H4)</f>
+        <v>10000</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46072</v>
+      </c>
+      <c r="E5" s="1">
+        <f xml:space="preserve"> D5 + (H5 / F5) * 7</f>
+        <v>46086</v>
+      </c>
       <c r="F5">
         <v>3000</v>
       </c>
+      <c r="G5">
+        <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
+        <v>2</v>
+      </c>
       <c r="H5">
         <v>6000</v>
+      </c>
+      <c r="I5">
+        <f ca="1">((F5)*(G5))-(H5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <f t="shared" ref="I4:I6" si="0">((F6)*(G6))-(H6)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B193A1D2-61BE-47C2-9755-78CE94C983D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71563C31-FD46-4291-B12B-4723013A03C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -468,8 +468,8 @@
         <v>46048</v>
       </c>
       <c r="E2" s="1">
-        <f xml:space="preserve"> D2 + (H2 / F2) * 7</f>
-        <v>48381.333333333336</v>
+        <f xml:space="preserve"> (D2 + (H2 / F2) * 7) - 1</f>
+        <v>48380.333333333336</v>
       </c>
       <c r="F2">
         <v>3000</v>
@@ -500,8 +500,8 @@
         <v>46020</v>
       </c>
       <c r="E3" s="1">
-        <f xml:space="preserve"> D3 + (H3 / F3) * 7</f>
-        <v>46069</v>
+        <f xml:space="preserve"> (D3 + (H3 / F3) * 7) - 1</f>
+        <v>46068</v>
       </c>
       <c r="F3">
         <v>3000</v>
@@ -529,8 +529,8 @@
         <v>45992</v>
       </c>
       <c r="E4" s="1">
-        <f xml:space="preserve"> D4 + (H4 / F4) * 7</f>
-        <v>46048</v>
+        <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) - 1</f>
+        <v>46047</v>
       </c>
       <c r="F4">
         <v>2000</v>
@@ -558,8 +558,8 @@
         <v>46072</v>
       </c>
       <c r="E5" s="1">
-        <f xml:space="preserve"> D5 + (H5 / F5) * 7</f>
-        <v>46086</v>
+        <f t="shared" si="0"/>
+        <v>46085</v>
       </c>
       <c r="F5">
         <v>3000</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I6">
-        <f t="shared" ref="I4:I6" si="0">((F6)*(G6))-(H6)</f>
+        <f t="shared" ref="I6" si="1">((F6)*(G6))-(H6)</f>
         <v>0</v>
       </c>
     </row>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71563C31-FD46-4291-B12B-4723013A03C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95CFF1C-3348-43D6-B0A7-BA507EE2EB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -468,8 +468,8 @@
         <v>46048</v>
       </c>
       <c r="E2" s="1">
-        <f xml:space="preserve"> (D2 + (H2 / F2) * 7) - 1</f>
-        <v>48380.333333333336</v>
+        <f xml:space="preserve"> D2 + (H2 / F2) * 7</f>
+        <v>48381.333333333336</v>
       </c>
       <c r="F2">
         <v>3000</v>
@@ -500,8 +500,8 @@
         <v>46020</v>
       </c>
       <c r="E3" s="1">
-        <f xml:space="preserve"> (D3 + (H3 / F3) * 7) - 1</f>
-        <v>46068</v>
+        <f t="shared" ref="E3:E5" si="0" xml:space="preserve"> D3 + (H3 / F3) * 7</f>
+        <v>46069</v>
       </c>
       <c r="F3">
         <v>3000</v>
@@ -529,8 +529,8 @@
         <v>45992</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) - 1</f>
-        <v>46047</v>
+        <f t="shared" si="0"/>
+        <v>46048</v>
       </c>
       <c r="F4">
         <v>2000</v>
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="F5">
         <v>3000</v>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95CFF1C-3348-43D6-B0A7-BA507EE2EB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EE3897-012B-4AAC-B610-94C1125EC566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -468,8 +468,8 @@
         <v>46048</v>
       </c>
       <c r="E2" s="1">
-        <f xml:space="preserve"> D2 + (H2 / F2) * 7</f>
-        <v>48381.333333333336</v>
+        <f xml:space="preserve"> (D2 + (H2 / F2) * 7) -1</f>
+        <v>48380.333333333336</v>
       </c>
       <c r="F2">
         <v>3000</v>
@@ -500,8 +500,8 @@
         <v>46020</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E5" si="0" xml:space="preserve"> D3 + (H3 / F3) * 7</f>
-        <v>46069</v>
+        <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
+        <v>46068</v>
       </c>
       <c r="F3">
         <v>3000</v>
@@ -529,8 +529,8 @@
         <v>45992</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" si="0"/>
-        <v>46048</v>
+        <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
+        <v>46047</v>
       </c>
       <c r="F4">
         <v>2000</v>
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="F5">
         <v>3000</v>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EE3897-012B-4AAC-B610-94C1125EC566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD126E7-5170-401F-9628-421ACABFB50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,9 +65,6 @@
     <t xml:space="preserve">сумма которая оплачена </t>
   </si>
   <si>
-    <t>Шамбер Алексей Вадимович</t>
-  </si>
-  <si>
     <t xml:space="preserve"> к оплате</t>
   </si>
   <si>
@@ -89,7 +86,10 @@
     <t>Minako Monster</t>
   </si>
   <si>
-    <t>Музохушаев Рахматулло Давлатбекович</t>
+    <t>Иванов Иван Иванович</t>
+  </si>
+  <si>
+    <t>Мирзохужаев Рахматулло Давлатбекович</t>
   </si>
 </sst>
 </file>
@@ -430,7 +430,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -451,12 +451,12 @@
         <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" s="1">
         <f xml:space="preserve"> (D2 + (H2 / F2) * 7) -1</f>
-        <v>48380.333333333336</v>
+        <v>46082</v>
       </c>
       <c r="F2">
         <v>3000</v>
@@ -479,22 +479,22 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <v>1000000</v>
+        <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>-985000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
       </c>
       <c r="D3" s="1">
         <v>46020</v>
@@ -520,10 +520,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1">
         <v>45992</v>
@@ -552,7 +552,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1">
         <v>46072</v>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD126E7-5170-401F-9628-421ACABFB50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF671363-FC52-4B4A-BD62-6D93E376B47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,14 +508,14 @@
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>21000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>6000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -530,17 +530,17 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>6000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF671363-FC52-4B4A-BD62-6D93E376B47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40978C00-B9D4-4A18-AF9F-F8503BFB6DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -530,7 +530,7 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46054</v>
+        <v>46055.75</v>
       </c>
       <c r="F4">
         <v>2000</v>
@@ -540,11 +540,11 @@
         <v>14</v>
       </c>
       <c r="H4">
-        <v>18000</v>
+        <v>18500</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>10000</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40978C00-B9D4-4A18-AF9F-F8503BFB6DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BD06E0-D9CE-4690-862E-91792137473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -530,7 +530,7 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46055.75</v>
+        <v>46054</v>
       </c>
       <c r="F4">
         <v>2000</v>
@@ -540,11 +540,11 @@
         <v>14</v>
       </c>
       <c r="H4">
-        <v>18500</v>
+        <v>18000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>9500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BD06E0-D9CE-4690-862E-91792137473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74746C72-6249-40D3-9883-35BDFF95D70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46068</v>
+        <v>46089</v>
       </c>
       <c r="F3">
         <v>3000</v>
@@ -511,11 +511,11 @@
         <v>10</v>
       </c>
       <c r="H3">
-        <v>21000</v>
+        <v>30000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>9000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74746C72-6249-40D3-9883-35BDFF95D70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABA3B20-6553-4355-87DE-C6A574651164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,14 +508,14 @@
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3">
         <v>30000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -530,17 +530,17 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46054</v>
+        <v>46061</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>6000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\Новая папка (5)\Happybike_site\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABA3B20-6553-4355-87DE-C6A574651164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501F6769-CE2C-4B46-8F90-7BEBE05A461D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>6000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,14 +508,14 @@
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>30000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -530,17 +530,17 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46061</v>
+        <v>46068</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
@@ -559,21 +559,21 @@
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>46085</v>
+        <v>46099</v>
       </c>
       <c r="F5">
         <v>3000</v>
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501F6769-CE2C-4B46-8F90-7BEBE05A461D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D424126F-7E1F-45B5-BDAC-13CF773F058F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D424126F-7E1F-45B5-BDAC-13CF773F058F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D74FD03-DA30-4B44-839F-3D6E7FE60DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,14 +508,14 @@
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3">
         <v>30000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -530,21 +530,21 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46068</v>
+        <v>46075</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H4">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>10000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D74FD03-DA30-4B44-839F-3D6E7FE60DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A417853-82D3-4CD7-BB8C-28F4F2EC95AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46089</v>
+        <v>46096</v>
       </c>
       <c r="F3">
         <v>3000</v>
@@ -511,11 +511,11 @@
         <v>14</v>
       </c>
       <c r="H3">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>12000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>6000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A417853-82D3-4CD7-BB8C-28F4F2EC95AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDD4239-E620-46AC-B9AF-68BDEE3EA86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,14 +508,14 @@
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>33000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>9000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -530,17 +530,17 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46075</v>
+        <v>46082</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4">
-        <v>24000</v>
+        <v>26000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDD4239-E620-46AC-B9AF-68BDEE3EA86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B86616-0AC9-4945-B4D0-A35A448B0F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>18000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -501,21 +501,21 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46096</v>
+        <v>46110</v>
       </c>
       <c r="F3">
         <v>3000</v>
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3">
-        <v>33000</v>
+        <v>39000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>12000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -537,14 +537,14 @@
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4">
         <v>26000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>12000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B86616-0AC9-4945-B4D0-A35A448B0F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED3283E-7ACF-4740-8E6D-CF6F414E36A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>21000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -501,17 +501,17 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46110</v>
+        <v>46124</v>
       </c>
       <c r="F3">
         <v>3000</v>
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3">
-        <v>39000</v>
+        <v>45000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
@@ -537,14 +537,14 @@
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4">
         <v>26000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>14000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED3283E-7ACF-4740-8E6D-CF6F414E36A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1C7079-CFFF-4087-9653-61099932F71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="2295" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>27000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,14 +508,14 @@
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3">
         <v>45000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>9000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -530,17 +530,17 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46082</v>
+        <v>46089</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>18000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1C7079-CFFF-4087-9653-61099932F71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3C61AE-CA7E-4C3B-B781-5DCECAE24026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="2295" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="F3">
         <v>3000</v>
@@ -511,11 +511,11 @@
         <v>19</v>
       </c>
       <c r="H3">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>12000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>21000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3C61AE-CA7E-4C3B-B781-5DCECAE24026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73366436-B8FD-4F1B-B6F2-9938E3448392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="2295" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,14 +476,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>30000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,14 +508,14 @@
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>48000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>9000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -530,21 +530,21 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46089</v>
+        <v>46096</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>18000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -566,14 +566,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>24000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73366436-B8FD-4F1B-B6F2-9938E3448392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8666A8F3-76EC-405E-870E-70962538C9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="2295" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>ФИО</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>Иванов Иван Иванович</t>
-  </si>
-  <si>
-    <t>Мирзохужаев Рахматулло Давлатбекович</t>
   </si>
 </sst>
 </file>
@@ -469,21 +466,21 @@
       </c>
       <c r="E2" s="1">
         <f xml:space="preserve"> (D2 + (H2 / F2) * 7) -1</f>
-        <v>46082</v>
+        <v>46222</v>
       </c>
       <c r="F2">
         <v>3000</v>
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>36000</v>
+        <v>-18000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,14 +505,14 @@
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3">
         <v>48000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>15000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -530,27 +527,24 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
-        <v>46096</v>
+        <v>46106.5</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>20000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -566,14 +560,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>27000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8666A8F3-76EC-405E-870E-70962538C9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF02545-BF4E-44A6-AA73-25ED1F6AC1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -473,14 +473,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <v>75000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>-18000</v>
+        <v>-15000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -498,21 +498,21 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="F3">
         <v>3000</v>
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>48000</v>
+        <v>54000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>21000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -534,14 +534,14 @@
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4">
         <v>33000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>21000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF02545-BF4E-44A6-AA73-25ED1F6AC1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A39C59-C636-45AB-8311-FEE67713AE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -473,14 +473,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>75000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>-15000</v>
+        <v>-12000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -498,21 +498,21 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="F3">
         <v>3000</v>
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>54000</v>
+        <v>60000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>18000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -534,14 +534,14 @@
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4">
         <v>33000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>23000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -560,14 +560,14 @@
       </c>
       <c r="G5">
         <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H5">
         <v>12000</v>
       </c>
       <c r="I5">
         <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>36000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A39C59-C636-45AB-8311-FEE67713AE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D127F9-A9FF-45B7-B202-F1A977BE5B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>ФИО</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Иванов Иван Иванович</t>
+  </si>
+  <si>
+    <t>Малкин Дмитрий Дмитриевич</t>
   </si>
 </sst>
 </file>
@@ -408,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.28515625" customWidth="1"/>
@@ -552,7 +555,7 @@
         <v>46072</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve"> (D5 + (H5 / F5) * 7) -1</f>
         <v>46099</v>
       </c>
       <c r="F5">
@@ -571,9 +574,43 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E6" s="1"/>
+      <c r="G6">
+        <f t="shared" ref="G6:G7" ca="1" si="1">CEILING((TODAY()-D6)/7,1)</f>
+        <v>6600</v>
+      </c>
       <c r="I6">
-        <f t="shared" ref="I6" si="1">((F6)*(G6))-(H6)</f>
+        <f t="shared" ref="I6:I7" ca="1" si="2">((F6)*(G6))-(H6)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46194</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" ref="E6:E7" si="3" xml:space="preserve"> (D7 + (H7 / F7) * 7) -1</f>
+        <v>46200</v>
+      </c>
+      <c r="F7">
+        <v>3000</v>
+      </c>
+      <c r="G7">
+        <f ca="1">CEILING((TODAY()-D7)/7,1)</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>3000</v>
+      </c>
+      <c r="I7">
+        <f ca="1">((F7)*(G7))-(H7)</f>
+        <v>-3000</v>
       </c>
     </row>
   </sheetData>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D127F9-A9FF-45B7-B202-F1A977BE5B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23863909-5446-469A-807B-BDE4BC591FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>ФИО</t>
   </si>
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46159</v>
+        <v>46173</v>
       </c>
       <c r="F3">
         <v>3000</v>
@@ -511,11 +511,11 @@
         <v>25</v>
       </c>
       <c r="H3">
-        <v>60000</v>
+        <v>66000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>15000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -529,7 +529,7 @@
         <v>45992</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
+        <f t="shared" ref="E4" si="0" xml:space="preserve"> (D4 + (H4 / F4) * 7) -1</f>
         <v>46106.5</v>
       </c>
       <c r="F4">
@@ -548,41 +548,11 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46072</v>
-      </c>
-      <c r="E5" s="1">
-        <f xml:space="preserve"> (D5 + (H5 / F5) * 7) -1</f>
-        <v>46099</v>
-      </c>
-      <c r="F5">
-        <v>3000</v>
-      </c>
-      <c r="G5">
-        <f ca="1">CEILING((TODAY()-D5)/7,1)</f>
-        <v>18</v>
-      </c>
-      <c r="H5">
-        <v>12000</v>
-      </c>
-      <c r="I5">
-        <f ca="1">((F5)*(G5))-(H5)</f>
-        <v>42000</v>
-      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E6" s="1"/>
-      <c r="G6">
-        <f t="shared" ref="G6:G7" ca="1" si="1">CEILING((TODAY()-D6)/7,1)</f>
-        <v>6600</v>
-      </c>
-      <c r="I6">
-        <f t="shared" ref="I6:I7" ca="1" si="2">((F6)*(G6))-(H6)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -595,7 +565,7 @@
         <v>46194</v>
       </c>
       <c r="E7" s="1">
-        <f t="shared" ref="E6:E7" si="3" xml:space="preserve"> (D7 + (H7 / F7) * 7) -1</f>
+        <f xml:space="preserve"> (D7 + (H7 / F7) * 7) -1</f>
         <v>46200</v>
       </c>
       <c r="F7">
@@ -603,14 +573,14 @@
       </c>
       <c r="G7">
         <f ca="1">CEILING((TODAY()-D7)/7,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>3000</v>
       </c>
       <c r="I7">
         <f ca="1">((F7)*(G7))-(H7)</f>
-        <v>-3000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23863909-5446-469A-807B-BDE4BC591FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF519382-F331-40F2-9677-FDFD776421C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>ФИО</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>Иванов Иван Иванович</t>
-  </si>
-  <si>
-    <t>Малкин Дмитрий Дмитриевич</t>
   </si>
 </sst>
 </file>
@@ -476,14 +473,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2">
         <v>75000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>-12000</v>
+        <v>-6000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -501,21 +498,21 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46173</v>
+        <v>46180</v>
       </c>
       <c r="F3">
         <v>3000</v>
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3">
-        <v>66000</v>
+        <v>69000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>9000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -537,14 +534,14 @@
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4">
         <v>33000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>25000</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -555,33 +552,8 @@
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46194</v>
-      </c>
-      <c r="E7" s="1">
-        <f xml:space="preserve"> (D7 + (H7 / F7) * 7) -1</f>
-        <v>46200</v>
-      </c>
-      <c r="F7">
-        <v>3000</v>
-      </c>
-      <c r="G7">
-        <f ca="1">CEILING((TODAY()-D7)/7,1)</f>
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>3000</v>
-      </c>
-      <c r="I7">
-        <f ca="1">((F7)*(G7))-(H7)</f>
-        <v>0</v>
-      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF519382-F331-40F2-9677-FDFD776421C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC552A5-F8F4-4BAD-BD45-13897972CC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,14 +473,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>75000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>-6000</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -498,17 +498,17 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="F3">
         <v>3000</v>
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>69000</v>
+        <v>72000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
@@ -534,14 +534,14 @@
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4">
         <v>33000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>29000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC552A5-F8F4-4BAD-BD45-13897972CC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5C2AB5-AF33-4D4E-B351-82B1B9E514E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46187</v>
+        <v>46215</v>
       </c>
       <c r="F3">
         <v>3000</v>
@@ -508,11 +508,11 @@
         <v>28</v>
       </c>
       <c r="H3">
-        <v>72000</v>
+        <v>84000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">

--- a/Baza.xlsx
+++ b/Baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titot\Desktop\happy_сайт\Happybike_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5C2AB5-AF33-4D4E-B351-82B1B9E514E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174ABC73-B8B2-4136-8741-CCD56C4A7A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="23775" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,14 +473,14 @@
       </c>
       <c r="G2">
         <f ca="1">CEILING((TODAY()-D2)/7,1)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>75000</v>
       </c>
       <c r="I2">
         <f ca="1">((F2)*(G2))-(H2)</f>
-        <v>-3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -498,17 +498,17 @@
       </c>
       <c r="E3" s="1">
         <f xml:space="preserve"> (D3 + (H3 / F3) * 7) -1</f>
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="F3">
         <v>3000</v>
       </c>
       <c r="G3">
         <f ca="1">CEILING((TODAY()-D3)/7,1)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>84000</v>
+        <v>87000</v>
       </c>
       <c r="I3">
         <f ca="1">((F3)*(G3))-(H3)</f>
@@ -534,14 +534,14 @@
       </c>
       <c r="G4">
         <f ca="1">CEILING((TODAY()-D4)/7,1)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4">
         <v>33000</v>
       </c>
       <c r="I4">
         <f ca="1">((F4)*(G4))-(H4)</f>
-        <v>31000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
